--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110555</v>
+        <v>110561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110561</v>
+        <v>110563</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110563</v>
+        <v>110564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110564</v>
+        <v>110570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110570</v>
+        <v>110574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110574</v>
+        <v>110576</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110576</v>
+        <v>110578</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110578</v>
+        <v>110591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110591</v>
+        <v>110593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110593</v>
+        <v>110599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110599</v>
+        <v>110621</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110621</v>
+        <v>110622</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110622</v>
+        <v>110627</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110627</v>
+        <v>110630</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110630</v>
+        <v>110636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110636</v>
+        <v>110637</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110637</v>
+        <v>110649</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110649</v>
+        <v>110650</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110650</v>
+        <v>110653</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110653</v>
+        <v>110655</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/S 548-2026 artfynd.xlsx
+++ b/artfynd/S 548-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136934578</v>
       </c>
       <c r="B2" t="n">
-        <v>110655</v>
+        <v>110659</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
